--- a/キャンペーン参加者.xlsx
+++ b/キャンペーン参加者.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ca2f93578f11a6ff/Desktop/Python/キャンペーン集計/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_27BF0D5005D78BEB5D521D29839CF49446BB46E9" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{D78EC68D-AA51-4126-B1EE-ECF033CDF847}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_27BF0D5005D78BEB5D521D29839CF49446BB46E9" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{26D3A1FF-6930-4EBD-BA17-E42A9CD81877}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -338,15 +338,9 @@
     <t>列範囲</t>
   </si>
   <si>
-    <t>A?D列</t>
-  </si>
-  <si>
     <t>集計結果の最終行まで罫線</t>
   </si>
   <si>
-    <t>F?G列</t>
-  </si>
-  <si>
     <t>サマリ最終行まで罫線</t>
   </si>
   <si>
@@ -381,6 +375,14 @@
   </si>
   <si>
     <t>金額表記ゆれはすべて正規化</t>
+  </si>
+  <si>
+    <t>A,D列</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F,G列</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -553,14 +555,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1459,7 +1461,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="14" t="s">
         <v>40</v>
       </c>
       <c r="B1" s="10"/>
@@ -2295,10 +2297,10 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
@@ -2308,10 +2310,10 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="3" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
@@ -2321,10 +2323,10 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
@@ -2343,7 +2345,7 @@
     </row>
     <row r="72" spans="1:7" ht="19.5" customHeight="1">
       <c r="A72" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B72" s="10"/>
       <c r="C72" s="10"/>
@@ -2367,10 +2369,10 @@
     </row>
     <row r="74" spans="1:7" ht="33" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
@@ -2388,22 +2390,22 @@
       <c r="G75" s="4"/>
     </row>
     <row r="76" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A76" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="B76" s="13"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="13"/>
-      <c r="E76" s="13"/>
-      <c r="F76" s="13"/>
-      <c r="G76" s="14"/>
+      <c r="A76" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B76" s="12"/>
+      <c r="C76" s="12"/>
+      <c r="D76" s="12"/>
+      <c r="E76" s="12"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="13"/>
     </row>
     <row r="77" spans="1:7" ht="33" customHeight="1">
       <c r="A77" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
@@ -2414,7 +2416,7 @@
     <row r="78" spans="1:7">
       <c r="A78" s="3"/>
       <c r="B78" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
@@ -2425,7 +2427,7 @@
     <row r="79" spans="1:7">
       <c r="A79" s="3"/>
       <c r="B79" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
@@ -2436,7 +2438,7 @@
     <row r="80" spans="1:7">
       <c r="A80" s="3"/>
       <c r="B80" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
@@ -2447,7 +2449,7 @@
     <row r="81" spans="1:7">
       <c r="A81" s="3"/>
       <c r="B81" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
@@ -2471,5 +2473,6 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/キャンペーン参加者.xlsx
+++ b/キャンペーン参加者.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ca2f93578f11a6ff/Desktop/Python/キャンペーン集計/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_27BF0D5005D78BEB5D521D29839CF49446BB46E9" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{26D3A1FF-6930-4EBD-BA17-E42A9CD81877}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_27BF0D5005D78BEB5D521D29839CF49446BB46E9" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{FC465947-0326-4C44-B94A-673FCC0BDAE8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="120">
   <si>
     <t>名前</t>
   </si>
@@ -877,7 +877,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="11" style="8" bestFit="1" customWidth="1"/>
@@ -1436,10 +1436,21 @@
         <v>980000</v>
       </c>
     </row>
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49">
+        <v>325000</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/キャンペーン参加者.xlsx
+++ b/キャンペーン参加者.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ca2f93578f11a6ff/Desktop/Python/キャンペーン集計/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_27BF0D5005D78BEB5D521D29839CF49446BB46E9" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{FC465947-0326-4C44-B94A-673FCC0BDAE8}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_27BF0D5005D78BEB5D521D29839CF49446BB46E9" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{FECE2BB0-8EA1-41B4-A9B4-530B2F3B8829}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2435,7 +2435,7 @@
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" ht="30" customHeight="1">
       <c r="A79" s="3"/>
       <c r="B79" s="3" t="s">
         <v>115</v>

--- a/キャンペーン参加者.xlsx
+++ b/キャンペーン参加者.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ca2f93578f11a6ff/Desktop/Python/キャンペーン集計/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_27BF0D5005D78BEB5D521D29839CF49446BB46E9" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{FECE2BB0-8EA1-41B4-A9B4-530B2F3B8829}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_D9920F4F3827CB378EF2B17C20482C5468BEA86C" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{319C854C-F6C4-4C69-A8BF-CB0112106506}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="17280" windowHeight="10665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="集計前" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="128">
   <si>
     <t>名前</t>
   </si>
@@ -65,72 +65,72 @@
     <t>2万円</t>
   </si>
   <si>
+    <t>中村葵</t>
+  </si>
+  <si>
+    <t>aoi.nakamura.work@example.com</t>
+  </si>
+  <si>
+    <t>1万円</t>
+  </si>
+  <si>
+    <t>daichi.yamamoto.alt@example.com</t>
+  </si>
+  <si>
+    <t>加藤結衣</t>
+  </si>
+  <si>
+    <t>kato.yui@example.com</t>
+  </si>
+  <si>
     <t>鈴木美咲</t>
   </si>
   <si>
     <t>suzuki.misaki@example.com</t>
   </si>
   <si>
-    <t>1万円</t>
-  </si>
-  <si>
-    <t>中村葵</t>
-  </si>
-  <si>
-    <t>aoi.nakamura.work@example.com</t>
-  </si>
-  <si>
-    <t>daichi.yamamoto.alt@example.com</t>
-  </si>
-  <si>
-    <t>加藤結衣</t>
-  </si>
-  <si>
-    <t>kato.yui@example.com</t>
-  </si>
-  <si>
     <t>佐藤陽菜</t>
   </si>
   <si>
+    <t>sato.hina@example.com</t>
+  </si>
+  <si>
+    <t>misaki.suzuki.alt@example.com</t>
+  </si>
+  <si>
+    <t>田中優</t>
+  </si>
+  <si>
+    <t>tanaka.yu@example.com</t>
+  </si>
+  <si>
+    <t>小林陽子</t>
+  </si>
+  <si>
+    <t>kobayashi.yoko@example.com</t>
+  </si>
+  <si>
+    <t>yoko.kobayashi.alt@example.com</t>
+  </si>
+  <si>
     <t>hina.sato.work@example.com</t>
   </si>
   <si>
-    <t>sato.hina@example.com</t>
-  </si>
-  <si>
-    <t>misaki.suzuki.alt@example.com</t>
-  </si>
-  <si>
-    <t>田中優</t>
-  </si>
-  <si>
-    <t>tanaka.yu@example.com</t>
+    <t>yui.kato.alt@example.com</t>
+  </si>
+  <si>
+    <t>yu.tanaka.alt@example.com</t>
   </si>
   <si>
     <t>ren.takahashi.alt@example.com</t>
   </si>
   <si>
-    <t>小林陽子</t>
-  </si>
-  <si>
-    <t>kobayashi.yoko@example.com</t>
-  </si>
-  <si>
     <t>hikaru.saito.alt@example.com</t>
   </si>
   <si>
     <t>nakamura.aoi@example.com</t>
   </si>
   <si>
-    <t>yoko.kobayashi.alt@example.com</t>
-  </si>
-  <si>
-    <t>yui.kato.alt@example.com</t>
-  </si>
-  <si>
-    <t>yu.tanaka.alt@example.com</t>
-  </si>
-  <si>
     <t>取り消し欄</t>
   </si>
   <si>
@@ -140,7 +140,22 @@
     <t>金額</t>
   </si>
   <si>
-    <t>取消</t>
+    <t>取消済</t>
+  </si>
+  <si>
+    <t>五七三零零零零</t>
+  </si>
+  <si>
+    <t>取消済予定</t>
+  </si>
+  <si>
+    <t>８８００００円</t>
+  </si>
+  <si>
+    <t>￥７２００００</t>
+  </si>
+  <si>
+    <t>一五零零零零零</t>
   </si>
   <si>
     <t>A1：キャンペーン参加者集計処理 仕様書</t>
@@ -188,7 +203,7 @@
     <t>B</t>
   </si>
   <si>
-    <t>ステータス（取消含む）</t>
+    <t>ステータス（取消済）</t>
   </si>
   <si>
     <t>C</t>
@@ -209,7 +224,7 @@
     <t>集計前シート読み込み</t>
   </si>
   <si>
-    <t>B列に「取消」を含む行を除外</t>
+    <t>B列が「取消済」の行を除外</t>
   </si>
   <si>
     <t>D列の金額を円（整数）に正規化</t>
@@ -230,7 +245,7 @@
     <t>集計後シートを新規作成</t>
   </si>
   <si>
-    <t>集計結果（A,D列）を書き込み</t>
+    <t>集計結果（A～D列）を書き込み</t>
   </si>
   <si>
     <t>D列を付与額ごとに色分け</t>
@@ -239,15 +254,18 @@
     <t>F,G列に付与額サマリを出力</t>
   </si>
   <si>
-    <t>A, B, C, D, F, G 列のみ自動調整</t>
-  </si>
-  <si>
-    <t>A,D列、F,G列に罫線設定</t>
+    <t>A,B,C,D,F,G列のみ自動調整</t>
+  </si>
+  <si>
+    <t>A～D列、F～G列に罫線設定</t>
   </si>
   <si>
     <t>見出しセルを太字化</t>
   </si>
   <si>
+    <t>保存前にバックアップ作成</t>
+  </si>
+  <si>
     <t>Excelファイルを保存</t>
   </si>
   <si>
@@ -275,6 +293,12 @@
     <t>数値化不可</t>
   </si>
   <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>数値化不可の場合は警告メッセージを出力</t>
+  </si>
+  <si>
     <t>付与額判定仕様</t>
   </si>
   <si>
@@ -338,9 +362,15 @@
     <t>列範囲</t>
   </si>
   <si>
+    <t>A~D列</t>
+  </si>
+  <si>
     <t>集計結果の最終行まで罫線</t>
   </si>
   <si>
+    <t>F~G列</t>
+  </si>
+  <si>
     <t>サマリ最終行まで罫線</t>
   </si>
   <si>
@@ -356,13 +386,10 @@
     <t>保存方法</t>
   </si>
   <si>
-    <t>元ファイル「キャンペーン参加者.xlsx」を上書き保存</t>
-  </si>
-  <si>
-    <t>備考</t>
-  </si>
-  <si>
-    <t>既存の『集計後』シートがある場合は削除してから再作成する</t>
+    <t>バックアップ作成後に元ファイルを上書き保存</t>
+  </si>
+  <si>
+    <t>既存の「集計後」シートがある場合は削除してから再作成する</t>
   </si>
   <si>
     <t>メール空白でも集計対象</t>
@@ -371,24 +398,22 @@
     <t>名前＋メールが同一の場合は金額合算</t>
   </si>
   <si>
-    <t>取消行は完全除外</t>
+    <t>取消済は完全除外</t>
   </si>
   <si>
     <t>金額表記ゆれはすべて正規化</t>
   </si>
   <si>
-    <t>A,D列</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>F,G列</t>
-    <phoneticPr fontId="1"/>
+    <t>Excelファイルはスクリプトと同一フォルダから取得する</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="6" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;\-#,##0"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <sz val="11"/>
@@ -523,7 +548,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -542,27 +567,33 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -877,11 +908,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="11" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.125" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -899,10 +931,10 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="7"/>
+      <c r="B2" s="6"/>
       <c r="C2" t="s">
         <v>12</v>
       </c>
@@ -911,74 +943,74 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="7"/>
+      <c r="B3" s="6"/>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3">
         <v>600000</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
         <v>26</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
       </c>
       <c r="D4">
         <v>1320000</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="7"/>
+      <c r="A5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="6"/>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D5">
         <v>1750000</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="7"/>
+      <c r="B6" s="6"/>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D6">
         <v>910000</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="7"/>
+      <c r="A7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="6"/>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D7">
         <v>650000</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="7"/>
+      <c r="A8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="6"/>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>1100000</v>
@@ -986,10 +1018,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D9">
         <v>780000</v>
@@ -1011,7 +1043,7 @@
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D11">
         <v>720000</v>
@@ -1022,7 +1054,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D12">
         <v>1400000</v>
@@ -1030,13 +1062,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" t="s">
         <v>26</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
       </c>
       <c r="D13">
         <v>880000</v>
@@ -1044,13 +1076,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14">
-        <v>605000</v>
+        <v>175000</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1061,26 +1093,26 @@
         <v>9</v>
       </c>
       <c r="D15">
-        <v>1880000</v>
+        <v>1920000</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16">
-        <v>1600000</v>
+        <v>35</v>
+      </c>
+      <c r="D16" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" t="s">
         <v>29</v>
-      </c>
-      <c r="C17" t="s">
-        <v>33</v>
       </c>
       <c r="D17">
         <v>700000</v>
@@ -1088,369 +1120,361 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D18">
-        <v>1300000</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D19">
-        <v>950000</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D20">
-        <v>1200000</v>
+        <v>1990000</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D21">
-        <v>1990000</v>
+        <v>640000</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D22">
-        <v>640000</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D23">
-        <v>940000</v>
+        <v>630000</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D24">
-        <v>630000</v>
+        <v>780000</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>27</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="C25" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D25">
-        <v>780000</v>
+        <v>1750000</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D26">
-        <v>1750000</v>
+        <v>610000</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="D27">
-        <v>610000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C28" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D28">
-        <v>2000000</v>
+        <v>820000</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D29">
-        <v>820000</v>
+        <v>720500</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C30" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D30">
-        <v>720500</v>
+        <v>1980000</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D31">
-        <v>1980000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C32" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D32">
-        <v>1500000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>8</v>
+        <v>14</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D33">
-        <v>810000</v>
+        <v>1020000</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>17</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
-        <v>32</v>
-      </c>
-      <c r="D34">
-        <v>1020000</v>
+        <v>29</v>
+      </c>
+      <c r="D34" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C35" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D35">
-        <v>880000</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D36">
-        <v>1800000</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D37">
-        <v>770000</v>
+        <v>910000</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>24</v>
-      </c>
-      <c r="D38">
-        <v>910000</v>
+        <v>12</v>
+      </c>
+      <c r="D38" s="10">
+        <v>600500</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C39" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D39">
-        <v>600500</v>
+        <v>700000</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C40" t="s">
-        <v>35</v>
-      </c>
-      <c r="D40">
-        <v>700000</v>
+        <v>21</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D41">
-        <v>720000</v>
+        <v>1450000</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D42">
-        <v>1450000</v>
+        <v>1900000</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D43">
-        <v>1900000</v>
+        <v>620000</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>29</v>
+        <v>18</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="C44" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D44">
-        <v>620000</v>
+        <v>890000</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>20</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C45" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="D45">
-        <v>890000</v>
+        <v>640500</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C46" t="s">
-        <v>6</v>
-      </c>
-      <c r="D46">
-        <v>640500</v>
+        <v>30</v>
+      </c>
+      <c r="D46" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D47">
-        <v>1500000</v>
+        <v>980000</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C48" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D48">
-        <v>980000</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" t="s">
-        <v>14</v>
-      </c>
-      <c r="C49" t="s">
-        <v>25</v>
-      </c>
-      <c r="D49">
         <v>325000</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
@@ -1459,28 +1483,28 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="22.625" style="6" customWidth="1"/>
-    <col min="2" max="3" width="28.625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="18.625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="3.625" style="6" customWidth="1"/>
-    <col min="6" max="7" width="18.625" style="6" customWidth="1"/>
-    <col min="8" max="9" width="9" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="6"/>
+    <col min="1" max="1" width="22.625" style="9" customWidth="1"/>
+    <col min="2" max="3" width="28.625" style="9" customWidth="1"/>
+    <col min="4" max="4" width="18.625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="3.625" style="9" customWidth="1"/>
+    <col min="6" max="7" width="18.625" style="9" customWidth="1"/>
+    <col min="8" max="15" width="9" style="9" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
+      <c r="A1" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="4"/>
@@ -1492,22 +1516,22 @@
       <c r="G2" s="4"/>
     </row>
     <row r="3" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A3" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
+      <c r="A3" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="2"/>
@@ -1517,10 +1541,10 @@
     </row>
     <row r="5" spans="1:7" ht="33" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="4"/>
@@ -1530,10 +1554,10 @@
     </row>
     <row r="6" spans="1:7" ht="33" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="4"/>
@@ -1543,10 +1567,10 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="4"/>
@@ -1564,25 +1588,25 @@
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A9" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
+      <c r="A9" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -1591,10 +1615,10 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>0</v>
@@ -1606,13 +1630,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -1621,10 +1645,10 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -1636,10 +1660,10 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>38</v>
@@ -1651,10 +1675,10 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>0</v>
@@ -1666,10 +1690,10 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -1681,10 +1705,10 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>2</v>
@@ -1696,10 +1720,10 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>3</v>
@@ -1719,22 +1743,22 @@
       <c r="G19" s="4"/>
     </row>
     <row r="20" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A20" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
+      <c r="A20" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -1747,7 +1771,7 @@
         <v>1</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -1760,7 +1784,7 @@
         <v>2</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -1773,7 +1797,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -1786,7 +1810,7 @@
         <v>4</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
@@ -1799,7 +1823,7 @@
         <v>5</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -1812,7 +1836,7 @@
         <v>6</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
@@ -1825,7 +1849,7 @@
         <v>7</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
@@ -1838,7 +1862,7 @@
         <v>8</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -1851,7 +1875,7 @@
         <v>9</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
@@ -1864,7 +1888,7 @@
         <v>10</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
@@ -1877,7 +1901,7 @@
         <v>11</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
@@ -1890,7 +1914,7 @@
         <v>12</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
@@ -1903,7 +1927,7 @@
         <v>13</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -1916,7 +1940,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
@@ -1929,7 +1953,7 @@
         <v>15</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -1938,54 +1962,54 @@
       <c r="G36" s="4"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
+      <c r="A37" s="3">
+        <v>16</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>81</v>
+      </c>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
     </row>
-    <row r="38" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A38" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
+    <row r="38" spans="1:7">
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+    </row>
+    <row r="39" spans="1:7" ht="19.5" customHeight="1">
+      <c r="A39" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B40" s="3">
-        <v>1234</v>
-      </c>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
+      <c r="A40" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B41" s="3">
         <v>1234</v>
@@ -1997,11 +2021,11 @@
       <c r="G41" s="4"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="5" t="s">
-        <v>81</v>
+      <c r="A42" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="B42" s="3">
-        <v>1234567</v>
+        <v>1234</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -2010,11 +2034,11 @@
       <c r="G42" s="4"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="3" t="s">
-        <v>82</v>
+      <c r="A43" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="B43" s="3">
-        <v>0</v>
+        <v>1234567</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -2024,7 +2048,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B44" s="3">
         <v>0</v>
@@ -2036,70 +2060,70 @@
       <c r="G44" s="4"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4"/>
+      <c r="A45" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B45" s="3">
+        <v>0</v>
+      </c>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
     </row>
-    <row r="46" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A46" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
+    <row r="46" spans="1:7" ht="33" customHeight="1">
+      <c r="A46" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="4"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+    </row>
+    <row r="48" spans="1:7" ht="19.5" customHeight="1">
+      <c r="A48" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" s="12"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B49" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
@@ -2109,10 +2133,10 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
@@ -2122,10 +2146,10 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="3" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
@@ -2134,67 +2158,71 @@
       <c r="G52" s="4"/>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="4"/>
-      <c r="B53" s="4"/>
+      <c r="A53" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
     </row>
-    <row r="54" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A54" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B54" s="10"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
+    <row r="54" spans="1:7">
+      <c r="A54" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B56" s="3" t="s">
+      <c r="A55" s="4"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+    </row>
+    <row r="56" spans="1:7" ht="19.5" customHeight="1">
+      <c r="A56" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B56" s="12"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58" s="4"/>
-      <c r="B58" s="4"/>
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -2202,11 +2230,11 @@
       <c r="G58" s="4"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>96</v>
+      <c r="A59" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
@@ -2215,12 +2243,8 @@
       <c r="G59" s="4"/>
     </row>
     <row r="60" spans="1:7">
-      <c r="A60" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>98</v>
-      </c>
+      <c r="A60" s="4"/>
+      <c r="B60" s="4"/>
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -2228,116 +2252,116 @@
       <c r="G60" s="4"/>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="4"/>
-      <c r="B61" s="4"/>
+      <c r="A61" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>104</v>
+      </c>
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
       <c r="G61" s="4"/>
     </row>
-    <row r="62" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A62" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="B62" s="10"/>
-      <c r="C62" s="10"/>
-      <c r="D62" s="10"/>
-      <c r="E62" s="10"/>
-      <c r="F62" s="10"/>
-      <c r="G62" s="10"/>
+    <row r="62" spans="1:7">
+      <c r="A62" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
     </row>
     <row r="63" spans="1:7">
-      <c r="A63" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>101</v>
-      </c>
+      <c r="A63" s="4"/>
+      <c r="B63" s="4"/>
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
       <c r="G63" s="4"/>
     </row>
-    <row r="64" spans="1:7">
-      <c r="A64" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
+    <row r="64" spans="1:7" ht="19.5" customHeight="1">
+      <c r="A64" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B64" s="12"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
     </row>
     <row r="65" spans="1:7">
-      <c r="A65" s="4"/>
-      <c r="B65" s="4"/>
+      <c r="A65" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>109</v>
+      </c>
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
     </row>
-    <row r="66" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A66" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="B66" s="10"/>
-      <c r="C66" s="10"/>
-      <c r="D66" s="10"/>
-      <c r="E66" s="10"/>
-      <c r="F66" s="10"/>
-      <c r="G66" s="10"/>
+    <row r="66" spans="1:7">
+      <c r="A66" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="A68" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
+      <c r="A67" s="4"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+    </row>
+    <row r="68" spans="1:7" ht="19.5" customHeight="1">
+      <c r="A68" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B68" s="12"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
+      <c r="A69" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
@@ -2346,99 +2370,103 @@
       <c r="G70" s="4"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="4"/>
-      <c r="B71" s="4"/>
+      <c r="A71" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
       <c r="G71" s="4"/>
     </row>
-    <row r="72" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A72" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="B72" s="10"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="10"/>
-      <c r="E72" s="10"/>
-      <c r="F72" s="10"/>
-      <c r="G72" s="10"/>
+    <row r="72" spans="1:7">
+      <c r="A72" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-    </row>
-    <row r="74" spans="1:7" ht="33" customHeight="1">
-      <c r="A74" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
+      <c r="A73" s="4"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
+    </row>
+    <row r="74" spans="1:7" ht="19.5" customHeight="1">
+      <c r="A74" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B74" s="12"/>
+      <c r="C74" s="12"/>
+      <c r="D74" s="12"/>
+      <c r="E74" s="12"/>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12"/>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="4"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="4"/>
-    </row>
-    <row r="76" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A76" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="B76" s="12"/>
-      <c r="C76" s="12"/>
-      <c r="D76" s="12"/>
-      <c r="E76" s="12"/>
-      <c r="F76" s="12"/>
-      <c r="G76" s="13"/>
-    </row>
-    <row r="77" spans="1:7" ht="33" customHeight="1">
-      <c r="A77" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
-      <c r="G77" s="3"/>
-    </row>
-    <row r="78" spans="1:7">
-      <c r="A78" s="3"/>
-      <c r="B78" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
-      <c r="G78" s="3"/>
-    </row>
-    <row r="79" spans="1:7" ht="30" customHeight="1">
-      <c r="A79" s="3"/>
+      <c r="A75" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+    </row>
+    <row r="76" spans="1:7" ht="33" customHeight="1">
+      <c r="A76" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" s="4"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+    </row>
+    <row r="78" spans="1:7" ht="19.5" customHeight="1">
+      <c r="A78" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B78" s="15"/>
+      <c r="C78" s="15"/>
+      <c r="D78" s="15"/>
+      <c r="E78" s="15"/>
+      <c r="F78" s="15"/>
+      <c r="G78" s="16"/>
+    </row>
+    <row r="79" spans="1:7" ht="33" customHeight="1">
+      <c r="A79" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="B79" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
@@ -2449,7 +2477,7 @@
     <row r="80" spans="1:7">
       <c r="A80" s="3"/>
       <c r="B80" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
@@ -2457,10 +2485,10 @@
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" ht="30" customHeight="1">
       <c r="A81" s="3"/>
       <c r="B81" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
@@ -2468,22 +2496,55 @@
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
     </row>
+    <row r="82" spans="1:7">
+      <c r="A82" s="3"/>
+      <c r="B82" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" s="3"/>
+      <c r="B83" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
+    </row>
+    <row r="84" spans="1:7" ht="33" customHeight="1">
+      <c r="A84" s="3"/>
+      <c r="B84" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+    </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A72:G72"/>
-    <mergeCell ref="A76:G76"/>
-    <mergeCell ref="A46:G46"/>
-    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="A78:G78"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A64:G64"/>
+    <mergeCell ref="A68:G68"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A74:G74"/>
     <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A56:G56"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A62:G62"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A48:G48"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/キャンペーン参加者.xlsx
+++ b/キャンペーン参加者.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ca2f93578f11a6ff/Desktop/Python/キャンペーン集計/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_D9920F4F3827CB378EF2B17C20482C5468BEA86C" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{319C854C-F6C4-4C69-A8BF-CB0112106506}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_9EDCAF43CB0F013FF6F33F1CCC4B2F54F83DE37C" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{73429814-9D67-4FF8-956F-B66AB0868D3A}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="17280" windowHeight="10665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="17280" windowHeight="10665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="集計前" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="129">
   <si>
     <t>名前</t>
   </si>
@@ -392,9 +392,6 @@
     <t>既存の「集計後」シートがある場合は削除してから再作成する</t>
   </si>
   <si>
-    <t>メール空白でも集計対象</t>
-  </si>
-  <si>
     <t>名前＋メールが同一の場合は金額合算</t>
   </si>
   <si>
@@ -405,6 +402,12 @@
   </si>
   <si>
     <t>Excelファイルはスクリプトと同一フォルダから取得する</t>
+  </si>
+  <si>
+    <t>名前とメールアドレスは必須入力</t>
+  </si>
+  <si>
+    <t>片方のみ入力されている場合はエラー終了</t>
   </si>
 </sst>
 </file>
@@ -580,14 +583,14 @@
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -908,7 +911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="11" style="7" bestFit="1" customWidth="1"/>
@@ -1120,24 +1123,22 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18">
-        <v>1200000</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="D18"/>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D19">
         <v>1200000</v>
@@ -1145,329 +1146,340 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D20">
-        <v>1990000</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D21">
-        <v>640000</v>
+        <v>1990000</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D22">
-        <v>250000</v>
+        <v>640000</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D23">
-        <v>630000</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D24">
-        <v>780000</v>
+        <v>630000</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D25">
-        <v>1750000</v>
+        <v>780000</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>27</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D26">
-        <v>610000</v>
+        <v>1750000</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="D27">
-        <v>2000000</v>
+        <v>610000</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D28">
-        <v>820000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D29">
-        <v>720500</v>
+        <v>820000</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D30">
-        <v>1980000</v>
+        <v>720500</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C31" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D31">
-        <v>1500000</v>
+        <v>1980000</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C32" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D32">
-        <v>90000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>14</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D33">
-        <v>1020000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>14</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
-      </c>
-      <c r="D34" t="s">
-        <v>42</v>
+        <v>35</v>
+      </c>
+      <c r="D34">
+        <v>1020000</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35">
-        <v>1800000</v>
+        <v>29</v>
+      </c>
+      <c r="D35" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C36" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D36">
-        <v>999999</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D37">
-        <v>910000</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
-      </c>
-      <c r="D38" s="10">
-        <v>600500</v>
+        <v>23</v>
+      </c>
+      <c r="D38">
+        <v>910000</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>32</v>
-      </c>
-      <c r="D39">
-        <v>700000</v>
+        <v>12</v>
+      </c>
+      <c r="D39" s="10">
+        <v>600500</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>43</v>
+        <v>32</v>
+      </c>
+      <c r="D40">
+        <v>700000</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C41" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41">
-        <v>1450000</v>
+        <v>21</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C42" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D42">
-        <v>1900000</v>
+        <v>1450000</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C43" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D43">
-        <v>620000</v>
+        <v>1900000</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>18</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C44" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D44">
-        <v>890000</v>
+        <v>620000</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>5</v>
+        <v>18</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="C45" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="D45">
-        <v>640500</v>
+        <v>890000</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C46" t="s">
-        <v>30</v>
-      </c>
-      <c r="D46" t="s">
-        <v>44</v>
+        <v>6</v>
+      </c>
+      <c r="D46">
+        <v>640500</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C47" t="s">
-        <v>17</v>
-      </c>
-      <c r="D47">
-        <v>980000</v>
+        <v>30</v>
+      </c>
+      <c r="D47" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48">
+        <v>980000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
         <v>20</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C49" t="s">
         <v>24</v>
       </c>
-      <c r="D48">
+      <c r="D49">
         <v>325000</v>
       </c>
     </row>
@@ -1483,7 +1495,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="22.625" style="9" customWidth="1"/>
@@ -1491,12 +1503,12 @@
     <col min="4" max="4" width="18.625" style="9" customWidth="1"/>
     <col min="5" max="5" width="3.625" style="9" customWidth="1"/>
     <col min="6" max="7" width="18.625" style="9" customWidth="1"/>
-    <col min="8" max="15" width="9" style="9" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="9"/>
+    <col min="8" max="17" width="9" style="9" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="13" t="s">
         <v>45</v>
       </c>
       <c r="B1" s="12"/>
@@ -1516,7 +1528,7 @@
       <c r="G2" s="4"/>
     </row>
     <row r="3" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="11" t="s">
         <v>46</v>
       </c>
       <c r="B3" s="12"/>
@@ -1588,7 +1600,7 @@
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="11" t="s">
         <v>55</v>
       </c>
       <c r="B9" s="12"/>
@@ -1743,7 +1755,7 @@
       <c r="G19" s="4"/>
     </row>
     <row r="20" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="11" t="s">
         <v>63</v>
       </c>
       <c r="B20" s="12"/>
@@ -1984,7 +1996,7 @@
       <c r="G38" s="4"/>
     </row>
     <row r="39" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A39" s="13" t="s">
+      <c r="A39" s="11" t="s">
         <v>82</v>
       </c>
       <c r="B39" s="12"/>
@@ -2095,7 +2107,7 @@
       <c r="G47" s="4"/>
     </row>
     <row r="48" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A48" s="13" t="s">
+      <c r="A48" s="11" t="s">
         <v>92</v>
       </c>
       <c r="B48" s="12"/>
@@ -2193,7 +2205,7 @@
       <c r="G55" s="4"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A56" s="13" t="s">
+      <c r="A56" s="11" t="s">
         <v>99</v>
       </c>
       <c r="B56" s="12"/>
@@ -2287,7 +2299,7 @@
       <c r="G63" s="4"/>
     </row>
     <row r="64" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A64" s="13" t="s">
+      <c r="A64" s="11" t="s">
         <v>107</v>
       </c>
       <c r="B64" s="12"/>
@@ -2333,7 +2345,7 @@
       <c r="G67" s="4"/>
     </row>
     <row r="68" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A68" s="13" t="s">
+      <c r="A68" s="11" t="s">
         <v>111</v>
       </c>
       <c r="B68" s="12"/>
@@ -2405,7 +2417,7 @@
       <c r="G73" s="4"/>
     </row>
     <row r="74" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A74" s="13" t="s">
+      <c r="A74" s="11" t="s">
         <v>119</v>
       </c>
       <c r="B74" s="12"/>
@@ -2477,7 +2489,7 @@
     <row r="80" spans="1:7">
       <c r="A80" s="3"/>
       <c r="B80" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
@@ -2485,10 +2497,10 @@
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
     </row>
-    <row r="81" spans="1:7" ht="30" customHeight="1">
+    <row r="81" spans="1:7" ht="33">
       <c r="A81" s="3"/>
       <c r="B81" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
@@ -2496,10 +2508,10 @@
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" ht="30" customHeight="1">
       <c r="A82" s="3"/>
       <c r="B82" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
@@ -2510,7 +2522,7 @@
     <row r="83" spans="1:7">
       <c r="A83" s="3"/>
       <c r="B83" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
@@ -2518,16 +2530,27 @@
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
     </row>
-    <row r="84" spans="1:7" ht="33" customHeight="1">
+    <row r="84" spans="1:7">
       <c r="A84" s="3"/>
       <c r="B84" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
+    </row>
+    <row r="85" spans="1:7" ht="33" customHeight="1">
+      <c r="A85" s="3"/>
+      <c r="B85" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2535,10 +2558,10 @@
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="A64:G64"/>
     <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A74:G74"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A56:G56"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A56:G56"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A39:G39"/>
     <mergeCell ref="A48:G48"/>

--- a/キャンペーン参加者.xlsx
+++ b/キャンペーン参加者.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ca2f93578f11a6ff/Desktop/Python/キャンペーン集計/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_9EDCAF43CB0F013FF6F33F1CCC4B2F54F83DE37C" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{73429814-9D67-4FF8-956F-B66AB0868D3A}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_3A18AD4E251F4886FC5DB7B5CCC82554C8353B7C" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{BBC7027D-6AC1-4AB2-B0A6-8E3B09A1B4E8}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="3120" windowWidth="17280" windowHeight="10665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -392,6 +392,12 @@
     <t>既存の「集計後」シートがある場合は削除してから再作成する</t>
   </si>
   <si>
+    <t>名前とメールアドレスは必須入力</t>
+  </si>
+  <si>
+    <t>片方のみ入力されている場合はエラー終了</t>
+  </si>
+  <si>
     <t>名前＋メールが同一の場合は金額合算</t>
   </si>
   <si>
@@ -402,12 +408,6 @@
   </si>
   <si>
     <t>Excelファイルはスクリプトと同一フォルダから取得する</t>
-  </si>
-  <si>
-    <t>名前とメールアドレスは必須入力</t>
-  </si>
-  <si>
-    <t>片方のみ入力されている場合はエラー終了</t>
   </si>
 </sst>
 </file>
@@ -583,14 +583,14 @@
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1503,12 +1503,12 @@
     <col min="4" max="4" width="18.625" style="9" customWidth="1"/>
     <col min="5" max="5" width="3.625" style="9" customWidth="1"/>
     <col min="6" max="7" width="18.625" style="9" customWidth="1"/>
-    <col min="8" max="17" width="9" style="9" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="9"/>
+    <col min="8" max="18" width="9" style="9" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="11" t="s">
         <v>45</v>
       </c>
       <c r="B1" s="12"/>
@@ -1528,7 +1528,7 @@
       <c r="G2" s="4"/>
     </row>
     <row r="3" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="13" t="s">
         <v>46</v>
       </c>
       <c r="B3" s="12"/>
@@ -1600,7 +1600,7 @@
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="13" t="s">
         <v>55</v>
       </c>
       <c r="B9" s="12"/>
@@ -1755,7 +1755,7 @@
       <c r="G19" s="4"/>
     </row>
     <row r="20" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="13" t="s">
         <v>63</v>
       </c>
       <c r="B20" s="12"/>
@@ -1996,7 +1996,7 @@
       <c r="G38" s="4"/>
     </row>
     <row r="39" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A39" s="11" t="s">
+      <c r="A39" s="13" t="s">
         <v>82</v>
       </c>
       <c r="B39" s="12"/>
@@ -2107,7 +2107,7 @@
       <c r="G47" s="4"/>
     </row>
     <row r="48" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A48" s="11" t="s">
+      <c r="A48" s="13" t="s">
         <v>92</v>
       </c>
       <c r="B48" s="12"/>
@@ -2205,7 +2205,7 @@
       <c r="G55" s="4"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A56" s="11" t="s">
+      <c r="A56" s="13" t="s">
         <v>99</v>
       </c>
       <c r="B56" s="12"/>
@@ -2299,7 +2299,7 @@
       <c r="G63" s="4"/>
     </row>
     <row r="64" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A64" s="11" t="s">
+      <c r="A64" s="13" t="s">
         <v>107</v>
       </c>
       <c r="B64" s="12"/>
@@ -2345,7 +2345,7 @@
       <c r="G67" s="4"/>
     </row>
     <row r="68" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A68" s="11" t="s">
+      <c r="A68" s="13" t="s">
         <v>111</v>
       </c>
       <c r="B68" s="12"/>
@@ -2417,7 +2417,7 @@
       <c r="G73" s="4"/>
     </row>
     <row r="74" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A74" s="11" t="s">
+      <c r="A74" s="13" t="s">
         <v>119</v>
       </c>
       <c r="B74" s="12"/>
@@ -2489,7 +2489,7 @@
     <row r="80" spans="1:7">
       <c r="A80" s="3"/>
       <c r="B80" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
@@ -2497,10 +2497,10 @@
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
     </row>
-    <row r="81" spans="1:7" ht="33">
+    <row r="81" spans="1:7" ht="33" customHeight="1">
       <c r="A81" s="3"/>
       <c r="B81" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
@@ -2508,10 +2508,10 @@
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
     </row>
-    <row r="82" spans="1:7" ht="30" customHeight="1">
+    <row r="82" spans="1:7">
       <c r="A82" s="3"/>
       <c r="B82" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
@@ -2522,7 +2522,7 @@
     <row r="83" spans="1:7">
       <c r="A83" s="3"/>
       <c r="B83" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
@@ -2533,7 +2533,7 @@
     <row r="84" spans="1:7">
       <c r="A84" s="3"/>
       <c r="B84" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
@@ -2544,7 +2544,7 @@
     <row r="85" spans="1:7" ht="33" customHeight="1">
       <c r="A85" s="3"/>
       <c r="B85" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
@@ -2558,10 +2558,10 @@
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="A64:G64"/>
     <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A74:G74"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A9:G9"/>
     <mergeCell ref="A56:G56"/>
-    <mergeCell ref="A9:G9"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A39:G39"/>
     <mergeCell ref="A48:G48"/>
